--- a/artfynd/A 7380-2023 artfynd.xlsx
+++ b/artfynd/A 7380-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7380-2023 artfynd.xlsx
+++ b/artfynd/A 7380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2277,6 +2277,150 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123763572</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6670</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100763</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cinnoberbagge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cucujus cinnaberinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norreda torp, N, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>663088</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634598</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Grov asplåga</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula # Grov asplåga</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7380-2023 artfynd.xlsx
+++ b/artfynd/A 7380-2023 artfynd.xlsx
@@ -2282,7 +2282,7 @@
         <v>123763572</v>
       </c>
       <c r="B15" t="n">
-        <v>6670</v>
+        <v>6672</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 7380-2023 artfynd.xlsx
+++ b/artfynd/A 7380-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7105584</v>
+        <v>111424050</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>37</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lagga kyrka, 4,5 km NO-ut, Upl</t>
+          <t>Norrsjön, Norrsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663097.2223093173</v>
+        <v>663091</v>
       </c>
       <c r="R2" t="n">
-        <v>6634671.765167279</v>
+        <v>6634680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,66 +771,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7105583</v>
+        <v>111611165</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>37</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Berk. &amp; Broome) Bas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lagga kyrka, 4,5 km NO-ut, Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663097.2223093173</v>
+        <v>663088</v>
       </c>
       <c r="R3" t="n">
-        <v>6634671.765167279</v>
+        <v>6634685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 ex. under ek och hassel.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,70 +878,66 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7105577</v>
+        <v>69962541</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>2075</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rutskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Xylobolus frustulatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Pers.:Fr.) Boidin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lagga kyrka, 4,6 km NO-ut, Upl</t>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663196.567369046</v>
+        <v>663099</v>
       </c>
       <c r="R4" t="n">
-        <v>6634833.252565511</v>
+        <v>6634764</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +964,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-01-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-01-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på naken ved på gammal eklåga, omkr. 253 cm.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,70 +985,82 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Naken ved på gammal eklåga. # Skogsek</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7105578</v>
+        <v>111611163</v>
       </c>
       <c r="B5" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223246</v>
+        <v>2975</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Bleknande kamskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Amanita lividopallescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Boud.) Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lagga kyrka, 4,6 km NO-ut, Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663186.0081420103</v>
+        <v>663205</v>
       </c>
       <c r="R5" t="n">
-        <v>6634798.040780992</v>
+        <v>6634821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,27 +1087,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Stammens omkrets= 54 cm</t>
+          <t>1 ex. under ek.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,37 +1106,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7105585</v>
+        <v>1162992</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,37 +1141,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lagga kyrka, 4,5 km NO-ut, Upl</t>
+          <t>300M SSÖ STORA NORET (11I7d02), Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663097.2223093173</v>
+        <v>663249</v>
       </c>
       <c r="R6" t="n">
-        <v>6634671.765167279</v>
+        <v>6634787</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,22 +1195,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>110873021 / DIC CAMP / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,70 +1216,75 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd / Lövskogslund</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gammal hassel</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thorleif Joelson, Henry Åkerström</t>
+          <t>Roine Schenning</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69962541</v>
+        <v>111611159</v>
       </c>
       <c r="B7" t="n">
-        <v>90568</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2075</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rutskinn</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Xylobolus frustulatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boidin</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663099.2241141999</v>
+        <v>663067</v>
       </c>
       <c r="R7" t="n">
-        <v>6634764.012249689</v>
+        <v>6634760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1296,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Knivsta</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1325,32 +1306,22 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Funbo</t>
+          <t>Lagga</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2006-01-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2006-01-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på naken ved på gammal eklåga, omkr. 253 cm.</t>
+          <t>På död, stående hassel.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,14 +1333,19 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Ung-/medelåldrig blandskog.</t>
+        </is>
+      </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Skogsek</t>
+          <t>Hassel</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Naken ved på gammal eklåga. # Skogsek</t>
+          <t>Död, stående hassel. # Hassel</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1380,58 +1356,61 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111424050</v>
+        <v>111611158</v>
       </c>
       <c r="B8" t="n">
-        <v>84741</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>4037</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Bolmörtsskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Entoloma sinuatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(Bull.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrsjön (Norrsjön), Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663091.3085779708</v>
+        <v>663128</v>
       </c>
       <c r="R8" t="n">
-        <v>6634680.066760574</v>
+        <v>6634761</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,19 +1440,14 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:28</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex. i lövförna under ek och hassel.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,58 +1458,58 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111611165</v>
+        <v>111611143</v>
       </c>
       <c r="B9" t="n">
-        <v>84741</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>37</v>
+        <v>4823</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättekamskivling</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amanita ceciliae</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Broome) Bas</t>
+          <t>(Kallenb.) Mikšík</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1549,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663088.0668624006</v>
+        <v>663065</v>
       </c>
       <c r="R9" t="n">
-        <v>6634684.960451891</v>
+        <v>6634728</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1538,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Uppsala</t>
+          <t>Knivsta</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1574,32 +1548,22 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Funbo</t>
+          <t>Lagga</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 ex. under ek och hassel.</t>
+          <t>2 ex. under hassel och gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,7 +1577,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
+          <t>Ung-/medelåldrig blandskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1624,22 +1588,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111611158</v>
+        <v>111611145</v>
       </c>
       <c r="B10" t="n">
-        <v>86021</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4037</v>
+        <v>4823</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bolmörtsskivling</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Entoloma sinuatum</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bull.) P.Kumm.</t>
+          <t>(Kallenb.) Mikšík</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1680,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663128.0992466732</v>
+        <v>663144</v>
       </c>
       <c r="R10" t="n">
-        <v>6634761.25188593</v>
+        <v>6634793</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,24 +1672,14 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 ex. i lövförna under ek och hassel.</t>
+          <t>1 ex. i lövförna under hassel.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,15 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111611138</v>
+        <v>111611146</v>
       </c>
       <c r="B11" t="n">
-        <v>81796</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,26 +1722,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5406</v>
+        <v>4823</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulmjölkig storskål</t>
+          <t>Hasselsopp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Peziza succosa</t>
+          <t>Leccinellum pseudoscabrum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Berk.</t>
+          <t>(Kallenb.) Mikšík</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1811,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663213.3366271106</v>
+        <v>663088</v>
       </c>
       <c r="R11" t="n">
-        <v>6634830.464506784</v>
+        <v>6634685</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,27 +1785,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>3 ex. på bar jord och i lövförna.</t>
+          <t>1 ex. under ek och hassel.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,22 +1820,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111611145</v>
+        <v>111611138</v>
       </c>
       <c r="B12" t="n">
-        <v>88630</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,26 +1838,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4823</v>
+        <v>5406</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hasselsopp</t>
+          <t>Gulmjölkig storskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leccinellum pseudoscabrum</t>
+          <t>Paragalactinia succosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kallenb.) Mikšík</t>
+          <t>(Berk.) Van Vooren</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1942,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663143.8264147732</v>
+        <v>663214</v>
       </c>
       <c r="R12" t="n">
-        <v>6634793.669287071</v>
+        <v>6634830</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,24 +1904,14 @@
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 ex. i lövförna under hassel.</t>
+          <t>3 ex. på bar jord och i lövförna.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,15 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111611146</v>
+        <v>105337280</v>
       </c>
       <c r="B13" t="n">
-        <v>88630</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4823</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hasselsopp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leccinellum pseudoscabrum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kallenb.) Mikšík</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2062,24 +1976,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+          <t>Stornoret, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663088.0668624006</v>
+        <v>663201</v>
       </c>
       <c r="R13" t="n">
-        <v>6634684.960451891</v>
+        <v>6634860</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,27 +2018,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 ex. under ek och hassel.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,58 +2044,48 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Vera Noest</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Vera Noest</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111611163</v>
+        <v>123763572</v>
       </c>
       <c r="B14" t="n">
-        <v>84766</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6675</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2975</v>
+        <v>100763</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bleknande kamskivling</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amanita lividopallescens</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Boud.) Kühner &amp; Romagn.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2195,21 +2095,31 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+          <t>Norreda torp, N, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>663206</v>
+        <v>663088</v>
       </c>
       <c r="R14" t="n">
-        <v>6634821</v>
+        <v>6634598</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2236,17 +2146,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 ex. under ek.</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,94 +2164,83 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Grov asplåga</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula # Grov asplåga</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123763572</v>
+        <v>3895870</v>
       </c>
       <c r="B15" t="n">
-        <v>6672</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100763</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norreda torp, N, Upl</t>
+          <t>300M SSÖ STORA NORET (11I7d02), Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663088</v>
+        <v>663249</v>
       </c>
       <c r="R15" t="n">
-        <v>6634598</v>
+        <v>6634787</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2370,12 +2264,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>1998-06-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>1998-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>110873021 / LATH VER / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,42 +2283,974 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Grov asplåga</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Populus tremula # Grov asplåga</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd / Lövskogslund</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Roine Schenning</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7105577</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,6 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>663197</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6634833</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7105584</v>
+      </c>
+      <c r="B17" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,5 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>663097</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6634672</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4986414</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>300M SSÖ STORA NORET (11I7d02), Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>663249</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6634787</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1998-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1998-06-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>110873021 / HEPA NOB / Tämligen allmän (2)  / OBJ.AREA:0,2 ha</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd / Lövskogslund</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Roine Schenning</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7105576</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,6 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>663181</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6634867</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7105583</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,5 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>663097</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6634672</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7105575</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,6 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>663181</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6634867</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7105585</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,5 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>663097</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6634672</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7105578</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,6 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>663186</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6634798</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stammens omkrets= 54 cm</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111611136</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91421</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>256754</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lundfingersvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramaria krieglsteineri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>663058</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6634838</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 ex. i vägkant, under ek, intill gran och hassel, (ingen lind i närheten).</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
